--- a/base_datos/solicitudes.xlsx
+++ b/base_datos/solicitudes.xlsx
@@ -52,7 +52,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -84,16 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -405,14 +402,14 @@
   <cols>
     <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
